--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20261022.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20261022.xlsx
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>99,950,442</t>
+          <t>84,787,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>84,787,000</t>
+          <t>99,950,442</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
